--- a/xls/square_16_quad4_13.xlsx
+++ b/xls/square_16_quad4_13.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>196</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>289</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>363</v>
+      </c>
+      <c r="I11">
+        <v>3.272331946167547</v>
+      </c>
+      <c r="J11">
+        <v>0.7056580059435561</v>
+      </c>
+      <c r="K11">
+        <v>1.1136599739442568</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>289</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>432</v>
+      </c>
+      <c r="I12">
+        <v>1.3754589612695243</v>
+      </c>
+      <c r="J12">
+        <v>-0.34287883485376813</v>
+      </c>
+      <c r="K12">
+        <v>0.20882294668145884</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>507</v>
       </c>
       <c r="I13">
-        <v>-0.950107959692242</v>
+        <v>-0.12927487802956564</v>
       </c>
       <c r="J13">
-        <v>-1.5329989896368708</v>
+        <v>-1.2720286873366282</v>
       </c>
       <c r="K13">
-        <v>-0.8863051259890916</v>
+        <v>-1.0114165955981693</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -517,13 +587,13 @@
         <v>588</v>
       </c>
       <c r="I14">
-        <v>-1.6449120215729618</v>
+        <v>-1.305156136722205</v>
       </c>
       <c r="J14">
-        <v>-1.6608929987256253</v>
+        <v>-1.3499091040716382</v>
       </c>
       <c r="K14">
-        <v>-1.2998369248445598</v>
+        <v>-1.263295187455712</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -552,13 +622,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>-1.6992717210049493</v>
+        <v>-1.3673113318743118</v>
       </c>
       <c r="J15">
-        <v>-1.7244286363295214</v>
+        <v>-1.4104841665720458</v>
       </c>
       <c r="K15">
-        <v>-1.3728250285849635</v>
+        <v>-1.33072698624056</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -587,13 +657,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.7751086065090222</v>
+        <v>-1.4396431100765874</v>
       </c>
       <c r="J16">
-        <v>-1.7933683408719379</v>
+        <v>-1.4971842934912842</v>
       </c>
       <c r="K16">
-        <v>-1.3922539765108621</v>
+        <v>-1.3621672718506213</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -622,13 +692,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.842442099275593</v>
+        <v>-1.4885867761940241</v>
       </c>
       <c r="J17">
-        <v>-1.7993321800492965</v>
+        <v>-1.5237363134002768</v>
       </c>
       <c r="K17">
-        <v>0.18701195018195718</v>
+        <v>1.1780727314577393</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -657,13 +727,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.9830403862950252</v>
+        <v>-1.5985823527346852</v>
       </c>
       <c r="J18">
-        <v>-1.6663575406484974</v>
+        <v>-1.524397419730649</v>
       </c>
       <c r="K18">
-        <v>2.864549548156303</v>
+        <v>3.3700223922960064</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.4108335560600003</v>
+        <v>-0.22779227001479047</v>
       </c>
       <c r="J19">
-        <v>-1.296574136969009</v>
+        <v>-0.22305847214742663</v>
       </c>
       <c r="K19">
-        <v>3.4507421233807976</v>
+        <v>4.842573791123725</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-0.06873167962102</v>
+        <v>-0.0022337562837188136</v>
       </c>
       <c r="J20">
-        <v>-0.07376407981165972</v>
+        <v>-0.002423452740804085</v>
       </c>
       <c r="K20">
-        <v>3.8032519785723795</v>
+        <v>4.087331505016005</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-0.051702156272572894</v>
+        <v>-0.0002635502789294156</v>
       </c>
       <c r="J21">
-        <v>-0.04469993638034325</v>
+        <v>-0.00022290219767779086</v>
       </c>
       <c r="K21">
-        <v>3.7038551019231005</v>
+        <v>3.5208673746171906</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.012139880512890345</v>
+        <v>-0.00014255144451132408</v>
       </c>
       <c r="J22">
-        <v>-0.010906763066663177</v>
+        <v>-0.000131697778207831</v>
       </c>
       <c r="K22">
-        <v>3.4375820788547284</v>
+        <v>3.452459269034112</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.005762715990914037</v>
+        <v>-3.994601178912807e-5</v>
       </c>
       <c r="J23">
-        <v>-0.004662173544566813</v>
+        <v>-3.242536311183858e-5</v>
       </c>
       <c r="K23">
-        <v>3.238852501153165</v>
+        <v>3.1163762815725624</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -867,13 +937,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.006849385424234034</v>
+        <v>-4.462066425975543e-5</v>
       </c>
       <c r="J24">
-        <v>-0.006300474290661221</v>
+        <v>-4.1066890784505806e-5</v>
       </c>
       <c r="K24">
-        <v>3.3292337299184602</v>
+        <v>3.2025146164810945</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -902,13 +972,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>2.6046087998859785e-6</v>
+        <v>1.0584799130092568e-8</v>
       </c>
       <c r="J25">
-        <v>-1.115833183688168e-6</v>
+        <v>-2.3295247807017546e-8</v>
       </c>
       <c r="K25">
-        <v>1.8301671760813891</v>
+        <v>1.831946445302458</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-1.3395501458519136e-5</v>
+        <v>-1.9930567447309856e-7</v>
       </c>
       <c r="J26">
-        <v>-1.3629168759515767e-5</v>
+        <v>-1.9950557405559933e-7</v>
       </c>
       <c r="K26">
-        <v>2.027962754225065</v>
+        <v>2.0830169248712878</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>1.6108247866886583e-6</v>
+        <v>1.5704605492662427e-8</v>
       </c>
       <c r="J27">
-        <v>-5.020498286413684e-7</v>
+        <v>-9.499656033344518e-9</v>
       </c>
       <c r="K27">
-        <v>1.6827402761659322</v>
+        <v>1.713539606890489</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-4.943123987032261e-7</v>
+        <v>-6.846359393517138e-9</v>
       </c>
       <c r="J28">
-        <v>-1.3243509054465256e-6</v>
+        <v>-2.0716495769357674e-8</v>
       </c>
       <c r="K28">
-        <v>1.6285581140970695</v>
+        <v>1.7028579828207617</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-1.3601149172063962e-6</v>
+        <v>-1.7153149645117094e-8</v>
       </c>
       <c r="J29">
-        <v>-1.4067470060422757e-6</v>
+        <v>-2.022146262876083e-8</v>
       </c>
       <c r="K29">
-        <v>1.5380420413701545</v>
+        <v>1.6118619307859463</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-1.0418610639478615e-6</v>
+        <v>-1.3415138430461455e-8</v>
       </c>
       <c r="J30">
-        <v>-9.597458385117042e-7</v>
+        <v>-1.3508868796946286e-8</v>
       </c>
       <c r="K30">
-        <v>1.4248076195820094</v>
+        <v>1.4868271462926073</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1112,13 +1182,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-6.495885962868817e-7</v>
+        <v>-8.376929223004733e-9</v>
       </c>
       <c r="J31">
-        <v>-7.144656874178715e-7</v>
+        <v>-9.99643218365596e-9</v>
       </c>
       <c r="K31">
-        <v>1.4038793918219685</v>
+        <v>1.4557680560206026</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1147,13 +1217,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-2.6187402437157e-7</v>
+        <v>-3.993869068577989e-9</v>
       </c>
       <c r="J32">
-        <v>-6.916949397506292e-7</v>
+        <v>-9.802256550623187e-9</v>
       </c>
       <c r="K32">
-        <v>1.489952689542373</v>
+        <v>1.5296583736526137</v>
       </c>
     </row>
   </sheetData>
